--- a/Taxas Antigas NTNB.xlsx
+++ b/Taxas Antigas NTNB.xlsx
@@ -127,9 +127,9 @@
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="ç­çº¿ Light"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Hang" typeface="ÃÂ«ÃÂ§ÃÂÃÂ¬ÃÂÃÂ ÃÂªÃÂ³ÃÂ ÃÂ«ÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂ§ÃÂ­ÃÂÃÂ§ÃÂºÃÂ¿ Light"/>
+        <a:font script="Hant" typeface="ÃÂ¦ÃÂÃÂ°ÃÂ§ÃÂ´ÃÂ°ÃÂ¦ÃÂÃÂÃÂ©ÃÂ«ÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -162,9 +162,9 @@
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="ç­çº¿"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Hang" typeface="ÃÂ«ÃÂ§ÃÂÃÂ¬ÃÂÃÂ ÃÂªÃÂ³ÃÂ ÃÂ«ÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂ§ÃÂ­ÃÂÃÂ§ÃÂºÃÂ¿"/>
+        <a:font script="Hant" typeface="ÃÂ¦ÃÂÃÂ°ÃÂ§ÃÂ´ÃÂ°ÃÂ¦ÃÂÃÂÃÂ©ÃÂ«ÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -346,10 +346,10 @@
   <dimension ref="C2:D10"/>
   <cols>
     <col min="3" max="3" customWidth="1" width="12"/>
-    <col min="4" max="4" customWidth="1" width="11.42578125"/>
+    <col min="4" max="4" customWidth="1" width="11.375"/>
   </cols>
   <sheetData>
-    <row r="2">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="C2" s="1">
         <v>46234</v>
       </c>
@@ -424,15 +424,15 @@
   <dimension ref="C2:AO10"/>
   <cols>
     <col min="3" max="3" customWidth="1" width="12"/>
-    <col min="4" max="4" customWidth="1" width="11.42578125"/>
-    <col min="24" max="24" customWidth="1" width="10.7109375"/>
-    <col min="28" max="28" customWidth="1" width="10.7109375"/>
-    <col min="32" max="32" customWidth="1" width="10.7109375"/>
-    <col min="36" max="36" customWidth="1" width="10.7109375"/>
-    <col min="40" max="40" customWidth="1" width="10.7109375"/>
+    <col min="4" max="4" customWidth="1" width="11.375"/>
+    <col min="24" max="24" customWidth="1" width="10.75"/>
+    <col min="28" max="28" customWidth="1" width="10.75"/>
+    <col min="32" max="32" customWidth="1" width="10.75"/>
+    <col min="36" max="36" customWidth="1" width="10.75"/>
+    <col min="40" max="40" customWidth="1" width="10.75"/>
   </cols>
   <sheetData>
-    <row r="2">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="C2" s="1">
         <v>46021</v>
       </c>
@@ -909,20 +909,80 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="C2:T11"/>
+  <dimension ref="C2:CD11"/>
   <cols>
-    <col min="3" max="3" customWidth="1" width="11.28515625"/>
-    <col min="7" max="7" customWidth="1" width="11.28515625"/>
-    <col min="11" max="11" customWidth="1" width="11.28515625"/>
-    <col min="15" max="15" customWidth="1" width="11.28515625"/>
+    <col min="3" max="3" customWidth="1" width="11.25"/>
+    <col min="7" max="7" customWidth="1" width="11.25"/>
+    <col min="11" max="11" customWidth="1" width="11.25"/>
+    <col min="15" max="15" customWidth="1" width="11.25"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="S2">
-        <v>46265</v>
-      </c>
-    </row>
-    <row r="3">
+    <row r="2" ht="16.5" customHeight="1">
+      <c r="S2" s="3">
+        <v>46080</v>
+      </c>
+      <c r="W2" s="3">
+        <v>46097</v>
+      </c>
+      <c r="AA2" s="3">
+        <v>46112</v>
+      </c>
+      <c r="AE2" s="3">
+        <v>46120</v>
+      </c>
+      <c r="AH2" s="3">
+        <v>46129</v>
+      </c>
+      <c r="AL2" s="3">
+        <v>46142</v>
+      </c>
+      <c r="AP2" s="3">
+        <v>46157</v>
+      </c>
+      <c r="AS2" s="3">
+        <v>46171</v>
+      </c>
+      <c r="AV2" s="3">
+        <v>46188</v>
+      </c>
+      <c r="AY2" s="3">
+        <v>46203</v>
+      </c>
+      <c r="BB2" s="3">
+        <v>46217</v>
+      </c>
+      <c r="BE2" s="3">
+        <v>46234</v>
+      </c>
+      <c r="BH2" s="3">
+        <v>46252</v>
+      </c>
+      <c r="BN2" s="3">
+        <v>46280</v>
+      </c>
+      <c r="BQ2" s="3">
+        <v>46287</v>
+      </c>
+      <c r="BS2">
+        <v>46276</v>
+      </c>
+      <c r="BU2">
+        <v>46279</v>
+      </c>
+      <c r="BW2">
+        <v>46281</v>
+      </c>
+      <c r="BY2">
+        <v>46282</v>
+      </c>
+      <c r="CA2">
+        <v>46283</v>
+      </c>
+      <c r="CC2">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1">
       <c r="C3" s="3">
         <v>46027</v>
       </c>
@@ -941,48 +1001,423 @@
       <c r="T3" t="str">
         <v>Taxa Atual</v>
       </c>
+      <c r="W3" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="X3" t="str">
+        <v>Taxa Atual</v>
+      </c>
+      <c r="AA3" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="AB3" t="str">
+        <v>Taxa Atual</v>
+      </c>
+      <c r="AE3" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="AF3" t="str">
+        <v>Taxa Atual</v>
+      </c>
+      <c r="AH3" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="AI3" t="str">
+        <v>Taxa Atual</v>
+      </c>
+      <c r="AL3" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="AM3" t="str">
+        <v>Taxa Atual</v>
+      </c>
+      <c r="AP3" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="AQ3" t="str">
+        <v>Taxa Atual</v>
+      </c>
+      <c r="AS3" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="AT3" t="str">
+        <v>Taxa Atual</v>
+      </c>
+      <c r="AV3" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="AW3" t="str">
+        <v>Taxa Atual</v>
+      </c>
+      <c r="AY3" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="AZ3" t="str">
+        <v>Taxa Atual</v>
+      </c>
+      <c r="BB3" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="BC3" t="str">
+        <v>Taxa Atual</v>
+      </c>
+      <c r="BE3" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="BF3" t="str">
+        <v>Taxa Atual</v>
+      </c>
+      <c r="BH3" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="BI3" t="str">
+        <v>Taxa Atual</v>
+      </c>
+      <c r="BK3" s="3">
+        <v>46265</v>
+      </c>
+      <c r="BN3" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="BO3" t="str">
+        <v>Taxa Atual</v>
+      </c>
+      <c r="BQ3" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="BR3" t="str">
+        <v>Taxa Atual</v>
+      </c>
+      <c r="BS3" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="BT3" t="str">
+        <v>Taxa Atual</v>
+      </c>
+      <c r="BU3" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="BV3" t="str">
+        <v>Taxa Atual</v>
+      </c>
+      <c r="BW3" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="BX3" t="str">
+        <v>Taxa Atual</v>
+      </c>
+      <c r="BY3" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="BZ3" t="str">
+        <v>Taxa Atual</v>
+      </c>
+      <c r="CA3" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="CB3" t="str">
+        <v>Taxa Atual</v>
+      </c>
+      <c r="CC3" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="CD3" t="str">
+        <v>Taxa Atual</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="S4" t="str">
         <v>NTNB 2028</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="2">
+        <v>0.0779</v>
+      </c>
+      <c r="W4" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="X4" s="2">
+        <v>0.0845</v>
+      </c>
+      <c r="AA4" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="AB4" s="2">
+        <v>0.078</v>
+      </c>
+      <c r="AE4" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="AF4" s="2">
+        <v>0.0779</v>
+      </c>
+      <c r="AH4" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="AI4" s="2">
+        <v>0.077</v>
+      </c>
+      <c r="AL4" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="AM4" s="2">
+        <v>0.0796</v>
+      </c>
+      <c r="AP4" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="AQ4" s="2">
+        <v>0.081</v>
+      </c>
+      <c r="AS4" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="AT4" s="2">
+        <v>0.0817</v>
+      </c>
+      <c r="AV4" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="AW4" s="2">
+        <v>0.0877</v>
+      </c>
+      <c r="AY4" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="AZ4" s="2">
+        <v>0.0889</v>
+      </c>
+      <c r="BB4" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="BC4" s="2">
+        <v>0.0855</v>
+      </c>
+      <c r="BE4" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="BF4" s="2">
+        <v>0.0847</v>
+      </c>
+      <c r="BH4" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="BI4" s="2">
+        <v>0.0822</v>
+      </c>
+      <c r="BK4" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="BL4" t="str">
+        <v>Taxa Atual</v>
+      </c>
+      <c r="BN4" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="BO4" s="2">
+        <v>0.0753</v>
+      </c>
+      <c r="BQ4" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="BR4" s="2">
+        <v>0.0742</v>
+      </c>
+      <c r="BS4" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="BT4">
+        <v>0.075343</v>
+      </c>
+      <c r="BU4" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="BV4">
+        <v>0.07515100000000001</v>
+      </c>
+      <c r="BW4" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="BX4">
+        <v>0.074712</v>
+      </c>
+      <c r="BY4" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="BZ4">
+        <v>0.073636</v>
+      </c>
+      <c r="CA4" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="CB4">
+        <v>0.0733</v>
+      </c>
+      <c r="CC4" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="CD4">
+        <v>0.07377600000000001</v>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="C5" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Taxa Atual</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Taxa Atual</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Taxa Atual</v>
+      </c>
+      <c r="O5" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="P5" t="str">
+        <v>Taxa Atual</v>
+      </c>
+      <c r="S5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="T5" s="2">
+        <v>0.0761</v>
+      </c>
+      <c r="W5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="X5" s="2">
+        <v>0.0825</v>
+      </c>
+      <c r="AA5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="AB5" s="2">
+        <v>0.0778</v>
+      </c>
+      <c r="AE5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="AF5" s="2">
+        <v>0.0775</v>
+      </c>
+      <c r="AH5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="AI5" s="2">
+        <v>0.0758</v>
+      </c>
+      <c r="AL5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="AM5" s="2">
+        <v>0.0785</v>
+      </c>
+      <c r="AP5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="AQ5" s="2">
+        <v>0.0804</v>
+      </c>
+      <c r="AS5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="AT5" s="2">
+        <v>0.0812</v>
+      </c>
+      <c r="AV5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="AW5" s="2">
+        <v>0.0859</v>
+      </c>
+      <c r="AY5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="AZ5" s="2">
+        <v>0.0864</v>
+      </c>
+      <c r="BB5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="BC5" s="2">
+        <v>0.0832</v>
+      </c>
+      <c r="BE5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="BF5" s="2">
+        <v>0.0823</v>
+      </c>
+      <c r="BH5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="BI5" s="2">
+        <v>0.0811</v>
+      </c>
+      <c r="BK5" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="BL5" s="2">
         <v>0.0794</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="C5" t="str">
-        <v>Papel</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Taxa Atual</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Papel</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Taxa Atual</v>
-      </c>
-      <c r="K5" t="str">
-        <v>Papel</v>
-      </c>
-      <c r="L5" t="str">
-        <v>Taxa Atual</v>
-      </c>
-      <c r="O5" t="str">
-        <v>Papel</v>
-      </c>
-      <c r="P5" t="str">
-        <v>Taxa Atual</v>
-      </c>
-      <c r="S5" t="str">
-        <v>NTNB 2029</v>
-      </c>
-      <c r="T5">
-        <v>0.079702</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="BN5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="BO5" s="2">
+        <v>0.0755</v>
+      </c>
+      <c r="BQ5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="BR5" s="2">
+        <v>0.074766</v>
+      </c>
+      <c r="BS5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="BT5">
+        <v>0.075099</v>
+      </c>
+      <c r="BU5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="BV5">
+        <v>0.075076</v>
+      </c>
+      <c r="BW5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="BX5">
+        <v>0.07503</v>
+      </c>
+      <c r="BY5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="BZ5">
+        <v>0.074062</v>
+      </c>
+      <c r="CA5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="CB5">
+        <v>0.073823</v>
+      </c>
+      <c r="CC5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="CD5">
+        <v>0.07434400000000001</v>
+      </c>
+    </row>
+    <row r="6" ht="18.75" customHeight="1">
       <c r="C6" t="str">
         <v>NTNB 2028</v>
       </c>
@@ -1010,11 +1445,137 @@
       <c r="S6" t="str">
         <v>NTNB 2030</v>
       </c>
-      <c r="T6">
-        <v>0.0812</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="T6" s="2">
+        <v>0.076</v>
+      </c>
+      <c r="W6" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="X6" s="2">
+        <v>0.0822</v>
+      </c>
+      <c r="AA6" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="AB6" s="2">
+        <v>0.0778</v>
+      </c>
+      <c r="AE6" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="AF6" s="2">
+        <v>0.0778</v>
+      </c>
+      <c r="AH6" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="AI6" s="2">
+        <v>0.076</v>
+      </c>
+      <c r="AL6" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="AM6" s="2">
+        <v>0.0789</v>
+      </c>
+      <c r="AP6" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="AQ6" s="2">
+        <v>0.0805</v>
+      </c>
+      <c r="AS6" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="AT6" s="2">
+        <v>0.0816</v>
+      </c>
+      <c r="AV6" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="AW6" s="2">
+        <v>0.0862</v>
+      </c>
+      <c r="AY6" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="AZ6" s="2">
+        <v>0.0863</v>
+      </c>
+      <c r="BB6" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="BC6" s="2">
+        <v>0.0833</v>
+      </c>
+      <c r="BE6" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="BF6" s="2">
+        <v>0.0828</v>
+      </c>
+      <c r="BH6" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="BI6" s="2">
+        <v>0.0818</v>
+      </c>
+      <c r="BK6" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="BL6" s="2">
+        <v>0.079702</v>
+      </c>
+      <c r="BN6" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="BO6" s="2">
+        <v>0.077</v>
+      </c>
+      <c r="BQ6" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="BR6" s="2">
+        <v>0.07655</v>
+      </c>
+      <c r="BS6" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="BT6">
+        <v>0.07586999999999999</v>
+      </c>
+      <c r="BU6" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="BV6">
+        <v>0.0761</v>
+      </c>
+      <c r="BW6" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="BX6">
+        <v>0.0765</v>
+      </c>
+      <c r="BY6" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="BZ6">
+        <v>0.07556</v>
+      </c>
+      <c r="CA6" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="CB6">
+        <v>0.0756</v>
+      </c>
+      <c r="CC6" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="CD6">
+        <v>0.076058</v>
+      </c>
+    </row>
+    <row r="7" ht="18.75" customHeight="1">
       <c r="C7" t="str">
         <v>NTNB 2029</v>
       </c>
@@ -1042,11 +1603,137 @@
       <c r="S7" t="str">
         <v>NTNB 2032</v>
       </c>
-      <c r="T7">
-        <v>0.0809</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="T7" s="2">
+        <v>0.0748</v>
+      </c>
+      <c r="W7" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="X7" s="2">
+        <v>0.0807</v>
+      </c>
+      <c r="AA7" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="AB7" s="2">
+        <v>0.0773</v>
+      </c>
+      <c r="AE7" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="AF7" s="2">
+        <v>0.0766</v>
+      </c>
+      <c r="AH7" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="AI7" s="2">
+        <v>0.0746</v>
+      </c>
+      <c r="AL7" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="AM7" s="2">
+        <v>0.0775</v>
+      </c>
+      <c r="AP7" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="AQ7" s="2">
+        <v>0.0793</v>
+      </c>
+      <c r="AS7" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="AT7" s="2">
+        <v>0.0803</v>
+      </c>
+      <c r="AV7" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="AW7" s="2">
+        <v>0.0847</v>
+      </c>
+      <c r="AY7" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="AZ7" s="2">
+        <v>0.0834</v>
+      </c>
+      <c r="BB7" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="BC7" s="2">
+        <v>0.0817</v>
+      </c>
+      <c r="BE7" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="BF7" s="2">
+        <v>0.0821</v>
+      </c>
+      <c r="BH7" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="BI7" s="2">
+        <v>0.0817</v>
+      </c>
+      <c r="BK7" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="BL7" s="2">
+        <v>0.0812</v>
+      </c>
+      <c r="BN7" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="BO7" s="2">
+        <v>0.0775</v>
+      </c>
+      <c r="BQ7" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="BR7" s="2">
+        <v>0.076431</v>
+      </c>
+      <c r="BS7" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="BT7">
+        <v>0.075816</v>
+      </c>
+      <c r="BU7" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="BV7">
+        <v>0.076483</v>
+      </c>
+      <c r="BW7" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="BX7">
+        <v>0.07685</v>
+      </c>
+      <c r="BY7" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="BZ7">
+        <v>0.076072</v>
+      </c>
+      <c r="CA7" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="CB7">
+        <v>0.076347</v>
+      </c>
+      <c r="CC7" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="CD7">
+        <v>0.076197</v>
+      </c>
+    </row>
+    <row r="8" ht="18.75" customHeight="1">
       <c r="C8" t="str">
         <v>NTNB 2030</v>
       </c>
@@ -1074,11 +1761,137 @@
       <c r="S8" t="str">
         <v>NTNB 2035</v>
       </c>
-      <c r="T8">
-        <v>0.079372</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="T8" s="2">
+        <v>0.0735</v>
+      </c>
+      <c r="W8" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="X8" s="2">
+        <v>0.0781</v>
+      </c>
+      <c r="AA8" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="AB8" s="2">
+        <v>0.076</v>
+      </c>
+      <c r="AE8" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="AF8" s="2">
+        <v>0.0752</v>
+      </c>
+      <c r="AH8" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="AI8" s="2">
+        <v>0.0729</v>
+      </c>
+      <c r="AL8" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="AM8" s="2">
+        <v>0.0758</v>
+      </c>
+      <c r="AP8" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="AQ8" s="2">
+        <v>0.0772</v>
+      </c>
+      <c r="AS8" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="AT8" s="2">
+        <v>0.0785</v>
+      </c>
+      <c r="AV8" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="AW8" s="2">
+        <v>0.0813</v>
+      </c>
+      <c r="AY8" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="AZ8" s="2">
+        <v>0.0816</v>
+      </c>
+      <c r="BB8" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="BC8" s="2">
+        <v>0.0805</v>
+      </c>
+      <c r="BE8" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="BF8" s="2">
+        <v>0.0809</v>
+      </c>
+      <c r="BH8" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="BI8" s="2">
+        <v>0.0802</v>
+      </c>
+      <c r="BK8" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="BL8" s="2">
+        <v>0.0809</v>
+      </c>
+      <c r="BN8" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="BO8" s="2">
+        <v>0.0772</v>
+      </c>
+      <c r="BQ8" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="BR8" s="2">
+        <v>0.076099</v>
+      </c>
+      <c r="BS8" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="BT8">
+        <v>0.075543</v>
+      </c>
+      <c r="BU8" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="BV8">
+        <v>0.076182</v>
+      </c>
+      <c r="BW8" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="BX8">
+        <v>0.07635900000000001</v>
+      </c>
+      <c r="BY8" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="BZ8">
+        <v>0.076111</v>
+      </c>
+      <c r="CA8" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="CB8">
+        <v>0.0764</v>
+      </c>
+      <c r="CC8" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="CD8">
+        <v>0.076169</v>
+      </c>
+    </row>
+    <row r="9" ht="19.5" customHeight="1">
       <c r="C9" t="str">
         <v>NTNB 2032</v>
       </c>
@@ -1106,8 +1919,134 @@
       <c r="S9" t="str">
         <v>NTNB 2045</v>
       </c>
-      <c r="T9">
-        <v>0.075538</v>
+      <c r="T9" s="2">
+        <v>0.0706</v>
+      </c>
+      <c r="W9" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="X9" s="2">
+        <v>0.0747</v>
+      </c>
+      <c r="AA9" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="AB9" s="2">
+        <v>0.0728</v>
+      </c>
+      <c r="AE9" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="AF9" s="2">
+        <v>0.072</v>
+      </c>
+      <c r="AH9" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="AI9" s="2">
+        <v>0.0704</v>
+      </c>
+      <c r="AL9" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="AM9" s="2">
+        <v>0.0724</v>
+      </c>
+      <c r="AP9" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="AQ9" s="2">
+        <v>0.0737</v>
+      </c>
+      <c r="AS9" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="AT9" s="2">
+        <v>0.0747</v>
+      </c>
+      <c r="AV9" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="AW9" s="2">
+        <v>0.0761</v>
+      </c>
+      <c r="AY9" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="AZ9" s="2">
+        <v>0.0775</v>
+      </c>
+      <c r="BB9" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="BC9" s="2">
+        <v>0.0758</v>
+      </c>
+      <c r="BE9" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="BF9" s="2">
+        <v>0.0765</v>
+      </c>
+      <c r="BH9" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="BI9" s="2">
+        <v>0.0761</v>
+      </c>
+      <c r="BK9" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="BL9" s="2">
+        <v>0.079372</v>
+      </c>
+      <c r="BN9" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="BO9" s="2">
+        <v>0.0747</v>
+      </c>
+      <c r="BQ9" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="BR9" s="2">
+        <v>0.0736</v>
+      </c>
+      <c r="BS9" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="BT9">
+        <v>0.073659</v>
+      </c>
+      <c r="BU9" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="BV9">
+        <v>0.0739</v>
+      </c>
+      <c r="BW9" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="BX9">
+        <v>0.074067</v>
+      </c>
+      <c r="BY9" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="BZ9">
+        <v>0.07381599999999999</v>
+      </c>
+      <c r="CA9" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="CB9">
+        <v>0.07400000000000001</v>
+      </c>
+      <c r="CC9" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="CD9">
+        <v>0.0738</v>
       </c>
     </row>
     <row r="10">
@@ -1134,6 +2073,12 @@
       </c>
       <c r="P10" s="2">
         <v>0.075</v>
+      </c>
+      <c r="BK10" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="BL10" s="2">
+        <v>0.075538</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -1165,7 +2110,7 @@
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="C2:T11"/>
+    <ignoredError numberStoredAsText="1" sqref="C2:CD11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Taxas Antigas NTNB.xlsx
+++ b/Taxas Antigas NTNB.xlsx
@@ -127,9 +127,9 @@
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
-        <a:font script="Hang" typeface="ÃÂÃÂ«ÃÂÃÂ§ÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂ ÃÂÃÂªÃÂÃÂ³ÃÂÃÂ ÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂ§ÃÂÃÂ­ÃÂÃÂÃÂÃÂ§ÃÂÃÂºÃÂÃÂ¿ Light"/>
-        <a:font script="Hant" typeface="ÃÂÃÂ¦ÃÂÃÂÃÂÃÂ°ÃÂÃÂ§ÃÂÃÂ´ÃÂÃÂ°ÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂ«ÃÂÃÂ"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂ¿ Light"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -162,9 +162,9 @@
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
-        <a:font script="Hang" typeface="ÃÂÃÂ«ÃÂÃÂ§ÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂ ÃÂÃÂªÃÂÃÂ³ÃÂÃÂ ÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂ§ÃÂÃÂ­ÃÂÃÂÃÂÃÂ§ÃÂÃÂºÃÂÃÂ¿"/>
-        <a:font script="Hant" typeface="ÃÂÃÂ¦ÃÂÃÂÃÂÃÂ°ÃÂÃÂ§ÃÂÃÂ´ÃÂÃÂ°ÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂ«ÃÂÃÂ"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂ¿"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -909,7 +909,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="C2:DE11"/>
+  <dimension ref="C2:DI11"/>
   <cols>
     <col min="3" max="3" customWidth="1" width="11.25"/>
     <col min="7" max="7" customWidth="1" width="11.25"/>
@@ -1014,6 +1014,12 @@
       <c r="DD2">
         <v>46302</v>
       </c>
+      <c r="DF2">
+        <v>46303</v>
+      </c>
+      <c r="DH2">
+        <v>46304</v>
+      </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="C3" s="3">
@@ -1229,6 +1235,18 @@
       <c r="DE3" t="str">
         <v>Taxa Atual</v>
       </c>
+      <c r="DF3" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="DG3" t="str">
+        <v>Taxa Atual</v>
+      </c>
+      <c r="DH3" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="DI3" t="str">
+        <v>Taxa Atual</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="X4" t="str">
@@ -1429,6 +1447,18 @@
       <c r="DE4">
         <v>0.068078</v>
       </c>
+      <c r="DF4" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="DG4">
+        <v>0.066846</v>
+      </c>
+      <c r="DH4" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="DI4">
+        <v>0.0668</v>
+      </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="C5" t="str">
@@ -1665,6 +1695,18 @@
       <c r="DE5">
         <v>0.067954</v>
       </c>
+      <c r="DF5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="DG5">
+        <v>0.06680799999999999</v>
+      </c>
+      <c r="DH5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="DI5">
+        <v>0.0664</v>
+      </c>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="C6" t="str">
@@ -1901,6 +1943,18 @@
       <c r="DE6">
         <v>0.068608</v>
       </c>
+      <c r="DF6" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="DG6">
+        <v>0.0675</v>
+      </c>
+      <c r="DH6" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="DI6">
+        <v>0.066723</v>
+      </c>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="C7" t="str">
@@ -2137,6 +2191,18 @@
       <c r="DE7">
         <v>0.068387</v>
       </c>
+      <c r="DF7" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="DG7">
+        <v>0.067454</v>
+      </c>
+      <c r="DH7" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="DI7">
+        <v>0.066841</v>
+      </c>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="C8" t="str">
@@ -2373,6 +2439,18 @@
       <c r="DE8">
         <v>0.068561</v>
       </c>
+      <c r="DF8" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="DG8">
+        <v>0.067576</v>
+      </c>
+      <c r="DH8" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="DI8">
+        <v>0.066922</v>
+      </c>
     </row>
     <row r="9" ht="19.5" customHeight="1">
       <c r="C9" t="str">
@@ -2608,6 +2686,18 @@
       </c>
       <c r="DE9">
         <v>0.067174</v>
+      </c>
+      <c r="DF9" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="DG9">
+        <v>0.066433</v>
+      </c>
+      <c r="DH9" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="DI9">
+        <v>0.06606</v>
       </c>
     </row>
     <row r="10">
@@ -2695,7 +2785,7 @@
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="C2:DE11"/>
+    <ignoredError numberStoredAsText="1" sqref="C2:DI11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Taxas Antigas NTNB.xlsx
+++ b/Taxas Antigas NTNB.xlsx
@@ -127,9 +127,9 @@
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂ¿ Light"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿ Light"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -162,9 +162,9 @@
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂ¿"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -909,7 +909,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="C2:DI11"/>
+  <dimension ref="C2:DK11"/>
   <cols>
     <col min="3" max="3" customWidth="1" width="11.25"/>
     <col min="7" max="7" customWidth="1" width="11.25"/>
@@ -1020,6 +1020,9 @@
       <c r="DH2">
         <v>46304</v>
       </c>
+      <c r="DJ2">
+        <v>46308</v>
+      </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="C3" s="3">
@@ -1247,6 +1250,12 @@
       <c r="DI3" t="str">
         <v>Taxa Atual</v>
       </c>
+      <c r="DJ3" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="DK3" t="str">
+        <v>Taxa Atual</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="X4" t="str">
@@ -1459,6 +1468,12 @@
       <c r="DI4">
         <v>0.0668</v>
       </c>
+      <c r="DJ4" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="DK4">
+        <v>0.067399</v>
+      </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="C5" t="str">
@@ -1707,6 +1722,12 @@
       <c r="DI5">
         <v>0.0664</v>
       </c>
+      <c r="DJ5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="DK5">
+        <v>0.06719599999999999</v>
+      </c>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="C6" t="str">
@@ -1955,6 +1976,12 @@
       <c r="DI6">
         <v>0.066723</v>
       </c>
+      <c r="DJ6" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="DK6">
+        <v>0.067494</v>
+      </c>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="C7" t="str">
@@ -2203,6 +2230,12 @@
       <c r="DI7">
         <v>0.066841</v>
       </c>
+      <c r="DJ7" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="DK7">
+        <v>0.067348</v>
+      </c>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="C8" t="str">
@@ -2451,6 +2484,12 @@
       <c r="DI8">
         <v>0.066922</v>
       </c>
+      <c r="DJ8" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="DK8">
+        <v>0.06756000000000001</v>
+      </c>
     </row>
     <row r="9" ht="19.5" customHeight="1">
       <c r="C9" t="str">
@@ -2698,6 +2737,12 @@
       </c>
       <c r="DI9">
         <v>0.06606</v>
+      </c>
+      <c r="DJ9" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="DK9">
+        <v>0.066568</v>
       </c>
     </row>
     <row r="10">
@@ -2785,7 +2830,7 @@
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="C2:DI11"/>
+    <ignoredError numberStoredAsText="1" sqref="C2:DK11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Taxas Antigas NTNB.xlsx
+++ b/Taxas Antigas NTNB.xlsx
@@ -127,9 +127,9 @@
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿ Light"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿ Light"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -162,9 +162,9 @@
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -909,7 +909,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="C2:DK11"/>
+  <dimension ref="C2:DO11"/>
   <cols>
     <col min="3" max="3" customWidth="1" width="11.25"/>
     <col min="7" max="7" customWidth="1" width="11.25"/>
@@ -1023,6 +1023,12 @@
       <c r="DJ2">
         <v>46308</v>
       </c>
+      <c r="DL2">
+        <v>46309</v>
+      </c>
+      <c r="DN2">
+        <v>46310</v>
+      </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="C3" s="3">
@@ -1256,6 +1262,18 @@
       <c r="DK3" t="str">
         <v>Taxa Atual</v>
       </c>
+      <c r="DL3" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="DM3" t="str">
+        <v>Taxa Atual</v>
+      </c>
+      <c r="DN3" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="DO3" t="str">
+        <v>Taxa Atual</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="X4" t="str">
@@ -1474,6 +1492,18 @@
       <c r="DK4">
         <v>0.067399</v>
       </c>
+      <c r="DL4" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="DM4">
+        <v>0.067262</v>
+      </c>
+      <c r="DN4" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="DO4">
+        <v>0.068055</v>
+      </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="C5" t="str">
@@ -1728,6 +1758,18 @@
       <c r="DK5">
         <v>0.06719599999999999</v>
       </c>
+      <c r="DL5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="DM5">
+        <v>0.0673</v>
+      </c>
+      <c r="DN5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="DO5">
+        <v>0.068</v>
+      </c>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="C6" t="str">
@@ -1982,6 +2024,18 @@
       <c r="DK6">
         <v>0.067494</v>
       </c>
+      <c r="DL6" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="DM6">
+        <v>0.067699</v>
+      </c>
+      <c r="DN6" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="DO6">
+        <v>0.068384</v>
+      </c>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="C7" t="str">
@@ -2236,6 +2290,18 @@
       <c r="DK7">
         <v>0.067348</v>
       </c>
+      <c r="DL7" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="DM7">
+        <v>0.067653</v>
+      </c>
+      <c r="DN7" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="DO7">
+        <v>0.068166</v>
+      </c>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="C8" t="str">
@@ -2490,6 +2556,18 @@
       <c r="DK8">
         <v>0.06756000000000001</v>
       </c>
+      <c r="DL8" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="DM8">
+        <v>0.06794</v>
+      </c>
+      <c r="DN8" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="DO8">
+        <v>0.068493</v>
+      </c>
     </row>
     <row r="9" ht="19.5" customHeight="1">
       <c r="C9" t="str">
@@ -2743,6 +2821,18 @@
       </c>
       <c r="DK9">
         <v>0.066568</v>
+      </c>
+      <c r="DL9" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="DM9">
+        <v>0.06726700000000001</v>
+      </c>
+      <c r="DN9" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="DO9">
+        <v>0.06787499999999999</v>
       </c>
     </row>
     <row r="10">
@@ -2830,7 +2920,7 @@
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="C2:DK11"/>
+    <ignoredError numberStoredAsText="1" sqref="C2:DO11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Taxas Antigas NTNB.xlsx
+++ b/Taxas Antigas NTNB.xlsx
@@ -127,9 +127,9 @@
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿ Light"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿ Light"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -162,9 +162,9 @@
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -909,7 +909,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="C2:DO11"/>
+  <dimension ref="C2:DU11"/>
   <cols>
     <col min="3" max="3" customWidth="1" width="11.25"/>
     <col min="7" max="7" customWidth="1" width="11.25"/>
@@ -1029,6 +1029,15 @@
       <c r="DN2">
         <v>46310</v>
       </c>
+      <c r="DP2">
+        <v>46311</v>
+      </c>
+      <c r="DR2">
+        <v>46314</v>
+      </c>
+      <c r="DT2">
+        <v>46315</v>
+      </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="C3" s="3">
@@ -1274,6 +1283,24 @@
       <c r="DO3" t="str">
         <v>Taxa Atual</v>
       </c>
+      <c r="DP3" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="DQ3" t="str">
+        <v>Taxa Atual</v>
+      </c>
+      <c r="DR3" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="DS3" t="str">
+        <v>Taxa Atual</v>
+      </c>
+      <c r="DT3" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="DU3" t="str">
+        <v>Taxa Atual</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="X4" t="str">
@@ -1504,6 +1531,24 @@
       <c r="DO4">
         <v>0.068055</v>
       </c>
+      <c r="DP4" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="DQ4">
+        <v>0.0689</v>
+      </c>
+      <c r="DR4" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="DS4">
+        <v>0.06926199999999999</v>
+      </c>
+      <c r="DT4" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="DU4">
+        <v>0.068459</v>
+      </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="C5" t="str">
@@ -1770,6 +1815,24 @@
       <c r="DO5">
         <v>0.068</v>
       </c>
+      <c r="DP5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="DQ5">
+        <v>0.06849999999999999</v>
+      </c>
+      <c r="DR5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="DS5">
+        <v>0.06860000000000001</v>
+      </c>
+      <c r="DT5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="DU5">
+        <v>0.067633</v>
+      </c>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="C6" t="str">
@@ -2036,6 +2099,24 @@
       <c r="DO6">
         <v>0.068384</v>
       </c>
+      <c r="DP6" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="DQ6">
+        <v>0.068822</v>
+      </c>
+      <c r="DR6" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="DS6">
+        <v>0.068858</v>
+      </c>
+      <c r="DT6" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="DU6">
+        <v>0.067961</v>
+      </c>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="C7" t="str">
@@ -2302,6 +2383,24 @@
       <c r="DO7">
         <v>0.068166</v>
       </c>
+      <c r="DP7" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="DQ7">
+        <v>0.06862700000000001</v>
+      </c>
+      <c r="DR7" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="DS7">
+        <v>0.06872</v>
+      </c>
+      <c r="DT7" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="DU7">
+        <v>0.068011</v>
+      </c>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="C8" t="str">
@@ -2568,6 +2667,24 @@
       <c r="DO8">
         <v>0.068493</v>
       </c>
+      <c r="DP8" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="DQ8">
+        <v>0.069</v>
+      </c>
+      <c r="DR8" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="DS8">
+        <v>0.069131</v>
+      </c>
+      <c r="DT8" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="DU8">
+        <v>0.068631</v>
+      </c>
     </row>
     <row r="9" ht="19.5" customHeight="1">
       <c r="C9" t="str">
@@ -2833,6 +2950,24 @@
       </c>
       <c r="DO9">
         <v>0.06787499999999999</v>
+      </c>
+      <c r="DP9" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="DQ9">
+        <v>0.06817000000000001</v>
+      </c>
+      <c r="DR9" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="DS9">
+        <v>0.06821100000000001</v>
+      </c>
+      <c r="DT9" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="DU9">
+        <v>0.067702</v>
       </c>
     </row>
     <row r="10">
@@ -2920,7 +3055,7 @@
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="C2:DO11"/>
+    <ignoredError numberStoredAsText="1" sqref="C2:DU11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Taxas Antigas NTNB.xlsx
+++ b/Taxas Antigas NTNB.xlsx
@@ -127,9 +127,9 @@
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿ Light"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿ Light"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -162,9 +162,9 @@
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -909,7 +909,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="C2:DU11"/>
+  <dimension ref="C2:DW11"/>
   <cols>
     <col min="3" max="3" customWidth="1" width="11.25"/>
     <col min="7" max="7" customWidth="1" width="11.25"/>
@@ -1038,6 +1038,9 @@
       <c r="DT2">
         <v>46315</v>
       </c>
+      <c r="DV2">
+        <v>46316</v>
+      </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="C3" s="3">
@@ -1301,6 +1304,12 @@
       <c r="DU3" t="str">
         <v>Taxa Atual</v>
       </c>
+      <c r="DV3" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="DW3" t="str">
+        <v>Taxa Atual</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="X4" t="str">
@@ -1549,6 +1558,12 @@
       <c r="DU4">
         <v>0.068459</v>
       </c>
+      <c r="DV4" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="DW4">
+        <v>0.0683</v>
+      </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="C5" t="str">
@@ -1833,6 +1848,12 @@
       <c r="DU5">
         <v>0.067633</v>
       </c>
+      <c r="DV5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="DW5">
+        <v>0.067429</v>
+      </c>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="C6" t="str">
@@ -2117,6 +2138,12 @@
       <c r="DU6">
         <v>0.067961</v>
       </c>
+      <c r="DV6" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="DW6">
+        <v>0.067834</v>
+      </c>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="C7" t="str">
@@ -2401,6 +2428,12 @@
       <c r="DU7">
         <v>0.068011</v>
       </c>
+      <c r="DV7" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="DW7">
+        <v>0.067916</v>
+      </c>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="C8" t="str">
@@ -2685,6 +2718,12 @@
       <c r="DU8">
         <v>0.068631</v>
       </c>
+      <c r="DV8" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="DW8">
+        <v>0.068274</v>
+      </c>
     </row>
     <row r="9" ht="19.5" customHeight="1">
       <c r="C9" t="str">
@@ -2968,6 +3007,12 @@
       </c>
       <c r="DU9">
         <v>0.067702</v>
+      </c>
+      <c r="DV9" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="DW9">
+        <v>0.066785</v>
       </c>
     </row>
     <row r="10">
@@ -3055,7 +3100,7 @@
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="C2:DU11"/>
+    <ignoredError numberStoredAsText="1" sqref="C2:DW11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Taxas Antigas NTNB.xlsx
+++ b/Taxas Antigas NTNB.xlsx
@@ -127,9 +127,9 @@
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿ Light"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿ Light"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -162,9 +162,9 @@
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -909,7 +909,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="C2:DW11"/>
+  <dimension ref="C2:DY11"/>
   <cols>
     <col min="3" max="3" customWidth="1" width="11.25"/>
     <col min="7" max="7" customWidth="1" width="11.25"/>
@@ -1041,6 +1041,9 @@
       <c r="DV2">
         <v>46316</v>
       </c>
+      <c r="DX2">
+        <v>46317</v>
+      </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="C3" s="3">
@@ -1310,6 +1313,12 @@
       <c r="DW3" t="str">
         <v>Taxa Atual</v>
       </c>
+      <c r="DX3" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="DY3" t="str">
+        <v>Taxa Atual</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="X4" t="str">
@@ -1564,6 +1573,12 @@
       <c r="DW4">
         <v>0.0683</v>
       </c>
+      <c r="DX4" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="DY4">
+        <v>0.06868</v>
+      </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="C5" t="str">
@@ -1854,6 +1869,12 @@
       <c r="DW5">
         <v>0.067429</v>
       </c>
+      <c r="DX5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="DY5">
+        <v>0.067458</v>
+      </c>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="C6" t="str">
@@ -2144,6 +2165,12 @@
       <c r="DW6">
         <v>0.067834</v>
       </c>
+      <c r="DX6" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="DY6">
+        <v>0.06765399999999999</v>
+      </c>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="C7" t="str">
@@ -2434,6 +2461,12 @@
       <c r="DW7">
         <v>0.067916</v>
       </c>
+      <c r="DX7" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="DY7">
+        <v>0.067668</v>
+      </c>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="C8" t="str">
@@ -2724,6 +2757,12 @@
       <c r="DW8">
         <v>0.068274</v>
       </c>
+      <c r="DX8" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="DY8">
+        <v>0.06777899999999999</v>
+      </c>
     </row>
     <row r="9" ht="19.5" customHeight="1">
       <c r="C9" t="str">
@@ -3013,6 +3052,12 @@
       </c>
       <c r="DW9">
         <v>0.066785</v>
+      </c>
+      <c r="DX9" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="DY9">
+        <v>0.066127</v>
       </c>
     </row>
     <row r="10">
@@ -3100,7 +3145,7 @@
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="C2:DW11"/>
+    <ignoredError numberStoredAsText="1" sqref="C2:DY11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Taxas Antigas NTNB.xlsx
+++ b/Taxas Antigas NTNB.xlsx
@@ -127,9 +127,9 @@
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿ Light"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿ Light"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -162,9 +162,9 @@
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -909,7 +909,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="C2:DY11"/>
+  <dimension ref="C2:EC11"/>
   <cols>
     <col min="3" max="3" customWidth="1" width="11.25"/>
     <col min="7" max="7" customWidth="1" width="11.25"/>
@@ -1044,6 +1044,12 @@
       <c r="DX2">
         <v>46317</v>
       </c>
+      <c r="DZ2">
+        <v>46318</v>
+      </c>
+      <c r="EB2">
+        <v>46321</v>
+      </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="C3" s="3">
@@ -1319,6 +1325,18 @@
       <c r="DY3" t="str">
         <v>Taxa Atual</v>
       </c>
+      <c r="DZ3" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="EA3" t="str">
+        <v>Taxa Atual</v>
+      </c>
+      <c r="EB3" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="EC3" t="str">
+        <v>Taxa Atual</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="X4" t="str">
@@ -1579,6 +1597,18 @@
       <c r="DY4">
         <v>0.06868</v>
       </c>
+      <c r="DZ4" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="EA4">
+        <v>0.068614</v>
+      </c>
+      <c r="EB4" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="EC4">
+        <v>0.079761</v>
+      </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="C5" t="str">
@@ -1875,6 +1905,18 @@
       <c r="DY5">
         <v>0.067458</v>
       </c>
+      <c r="DZ5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="EA5">
+        <v>0.0675</v>
+      </c>
+      <c r="EB5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="EC5">
+        <v>0.079093</v>
+      </c>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="C6" t="str">
@@ -2171,6 +2213,18 @@
       <c r="DY6">
         <v>0.06765399999999999</v>
       </c>
+      <c r="DZ6" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="EA6">
+        <v>0.0673</v>
+      </c>
+      <c r="EB6" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="EC6">
+        <v>0.079624</v>
+      </c>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="C7" t="str">
@@ -2467,6 +2521,18 @@
       <c r="DY7">
         <v>0.067668</v>
       </c>
+      <c r="DZ7" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="EA7">
+        <v>0.0672</v>
+      </c>
+      <c r="EB7" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="EC7">
+        <v>0.07995000000000001</v>
+      </c>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="C8" t="str">
@@ -2763,6 +2829,18 @@
       <c r="DY8">
         <v>0.06777899999999999</v>
       </c>
+      <c r="DZ8" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="EA8">
+        <v>0.06723499999999999</v>
+      </c>
+      <c r="EB8" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="EC8">
+        <v>0.080342</v>
+      </c>
     </row>
     <row r="9" ht="19.5" customHeight="1">
       <c r="C9" t="str">
@@ -3058,6 +3136,18 @@
       </c>
       <c r="DY9">
         <v>0.066127</v>
+      </c>
+      <c r="DZ9" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="EA9">
+        <v>0.06511700000000001</v>
+      </c>
+      <c r="EB9" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="EC9">
+        <v>0.076889</v>
       </c>
     </row>
     <row r="10">
@@ -3145,7 +3235,7 @@
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="C2:DY11"/>
+    <ignoredError numberStoredAsText="1" sqref="C2:EC11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Taxas Antigas NTNB.xlsx
+++ b/Taxas Antigas NTNB.xlsx
@@ -127,9 +127,9 @@
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿ Light"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿ Light"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -162,9 +162,9 @@
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -909,7 +909,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="C2:EC11"/>
+  <dimension ref="C2:EG11"/>
   <cols>
     <col min="3" max="3" customWidth="1" width="11.25"/>
     <col min="7" max="7" customWidth="1" width="11.25"/>
@@ -1050,6 +1050,12 @@
       <c r="EB2">
         <v>46321</v>
       </c>
+      <c r="ED2">
+        <v>46322</v>
+      </c>
+      <c r="EF2">
+        <v>46323</v>
+      </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="C3" s="3">
@@ -1337,6 +1343,18 @@
       <c r="EC3" t="str">
         <v>Taxa Atual</v>
       </c>
+      <c r="ED3" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="EE3" t="str">
+        <v>Taxa Atual</v>
+      </c>
+      <c r="EF3" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="EG3" t="str">
+        <v>Taxa Atual</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="X4" t="str">
@@ -1609,6 +1627,18 @@
       <c r="EC4">
         <v>0.079761</v>
       </c>
+      <c r="ED4" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="EE4">
+        <v>0.078255</v>
+      </c>
+      <c r="EF4" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="EG4">
+        <v>0.0781</v>
+      </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="C5" t="str">
@@ -1917,6 +1947,18 @@
       <c r="EC5">
         <v>0.079093</v>
       </c>
+      <c r="ED5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="EE5">
+        <v>0.077643</v>
+      </c>
+      <c r="EF5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="EG5">
+        <v>0.078125</v>
+      </c>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="C6" t="str">
@@ -2225,6 +2267,18 @@
       <c r="EC6">
         <v>0.079624</v>
       </c>
+      <c r="ED6" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="EE6">
+        <v>0.078245</v>
+      </c>
+      <c r="EF6" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="EG6">
+        <v>0.078804</v>
+      </c>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="C7" t="str">
@@ -2533,6 +2587,18 @@
       <c r="EC7">
         <v>0.07995000000000001</v>
       </c>
+      <c r="ED7" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="EE7">
+        <v>0.0786</v>
+      </c>
+      <c r="EF7" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="EG7">
+        <v>0.0791</v>
+      </c>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="C8" t="str">
@@ -2841,6 +2907,18 @@
       <c r="EC8">
         <v>0.080342</v>
       </c>
+      <c r="ED8" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="EE8">
+        <v>0.078246</v>
+      </c>
+      <c r="EF8" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="EG8">
+        <v>0.0786</v>
+      </c>
     </row>
     <row r="9" ht="19.5" customHeight="1">
       <c r="C9" t="str">
@@ -3148,6 +3226,18 @@
       </c>
       <c r="EC9">
         <v>0.076889</v>
+      </c>
+      <c r="ED9" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="EE9">
+        <v>0.074212</v>
+      </c>
+      <c r="EF9" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="EG9">
+        <v>0.07459500000000001</v>
       </c>
     </row>
     <row r="10">
@@ -3235,7 +3325,7 @@
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="C2:EC11"/>
+    <ignoredError numberStoredAsText="1" sqref="C2:EG11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Taxas Antigas NTNB.xlsx
+++ b/Taxas Antigas NTNB.xlsx
@@ -127,9 +127,9 @@
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿ Light"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿ Light"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -162,9 +162,9 @@
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -909,7 +909,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="C2:EG11"/>
+  <dimension ref="C2:EI11"/>
   <cols>
     <col min="3" max="3" customWidth="1" width="11.25"/>
     <col min="7" max="7" customWidth="1" width="11.25"/>
@@ -1056,6 +1056,9 @@
       <c r="EF2">
         <v>46323</v>
       </c>
+      <c r="EH2">
+        <v>46324</v>
+      </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="C3" s="3">
@@ -1355,6 +1358,12 @@
       <c r="EG3" t="str">
         <v>Taxa Atual</v>
       </c>
+      <c r="EH3" t="str">
+        <v>Papel</v>
+      </c>
+      <c r="EI3" t="str">
+        <v>Taxa Atual</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="X4" t="str">
@@ -1639,6 +1648,12 @@
       <c r="EG4">
         <v>0.0781</v>
       </c>
+      <c r="EH4" t="str">
+        <v>NTNB 2028</v>
+      </c>
+      <c r="EI4">
+        <v>0.07695400000000001</v>
+      </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="C5" t="str">
@@ -1959,6 +1974,12 @@
       <c r="EG5">
         <v>0.078125</v>
       </c>
+      <c r="EH5" t="str">
+        <v>NTNB 2029</v>
+      </c>
+      <c r="EI5">
+        <v>0.07781500000000001</v>
+      </c>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="C6" t="str">
@@ -2279,6 +2300,12 @@
       <c r="EG6">
         <v>0.078804</v>
       </c>
+      <c r="EH6" t="str">
+        <v>NTNB 2030</v>
+      </c>
+      <c r="EI6">
+        <v>0.078536</v>
+      </c>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="C7" t="str">
@@ -2599,6 +2626,12 @@
       <c r="EG7">
         <v>0.0791</v>
       </c>
+      <c r="EH7" t="str">
+        <v>NTNB 2032</v>
+      </c>
+      <c r="EI7">
+        <v>0.078798</v>
+      </c>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="C8" t="str">
@@ -2919,6 +2952,12 @@
       <c r="EG8">
         <v>0.0786</v>
       </c>
+      <c r="EH8" t="str">
+        <v>NTNB 2035</v>
+      </c>
+      <c r="EI8">
+        <v>0.07876999999999999</v>
+      </c>
     </row>
     <row r="9" ht="19.5" customHeight="1">
       <c r="C9" t="str">
@@ -3238,6 +3277,12 @@
       </c>
       <c r="EG9">
         <v>0.07459500000000001</v>
+      </c>
+      <c r="EH9" t="str">
+        <v>NTNB 2045</v>
+      </c>
+      <c r="EI9">
+        <v>0.075</v>
       </c>
     </row>
     <row r="10">
@@ -3325,7 +3370,7 @@
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="C2:EG11"/>
+    <ignoredError numberStoredAsText="1" sqref="C2:EI11"/>
   </ignoredErrors>
 </worksheet>
 </file>